--- a/Data/useCarDaten.xlsx
+++ b/Data/useCarDaten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dulen\OneDrive\Music\Dokumente\Organisation\Etudes\Studium_Projekt\BA_KI_preisprognose\Bachelorarbeit_KI_preissystem\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35067e63d4c6ea04/Music/Dokumente/Organisation/Etudes/Studium_Projekt/BA_KI_preisprognose/Bachelorarbeit_KI_preissystem/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B7B4D9-0986-4EA9-9F96-6634871DF372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{08B7B4D9-0986-4EA9-9F96-6634871DF372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ADC67FF-6D7F-4A44-B891-E08569EB8722}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E056EEA4-8F88-4AFD-AB7C-FC3599D22606}"/>
+    <workbookView xWindow="-19310" yWindow="-1320" windowWidth="19420" windowHeight="10300" xr2:uid="{E056EEA4-8F88-4AFD-AB7C-FC3599D22606}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1 (2)" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="A">Tabelle1!$SXG$10</definedName>
-    <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">'Tabelle1 (2)'!$A$1:$AB$40</definedName>
+    <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">'Tabelle1 (2)'!$A$1:$AB$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="210">
   <si>
     <t>Transmission type</t>
   </si>
@@ -661,6 +661,24 @@
   </si>
   <si>
     <t>A39</t>
+  </si>
+  <si>
+    <t>Cabrio Lounge</t>
+  </si>
+  <si>
+    <t>Benzin</t>
+  </si>
+  <si>
+    <t>carbrio</t>
+  </si>
+  <si>
+    <t>A40</t>
+  </si>
+  <si>
+    <t>A50</t>
+  </si>
+  <si>
+    <t>A60</t>
   </si>
 </sst>
 </file>
@@ -769,16 +787,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="79">
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2033,6 +2048,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2152,8 +2170,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FBE7D9C5-43D3-4492-ADEE-DDA6D2AEC0A3}" name="Tabelle1_1" displayName="Tabelle1_1" ref="A1:AC40" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:AC40" xr:uid="{FBE7D9C5-43D3-4492-ADEE-DDA6D2AEC0A3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FBE7D9C5-43D3-4492-ADEE-DDA6D2AEC0A3}" name="Tabelle1_1" displayName="Tabelle1_1" ref="A1:AC43" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:AC43" xr:uid="{FBE7D9C5-43D3-4492-ADEE-DDA6D2AEC0A3}"/>
   <tableColumns count="29">
     <tableColumn id="1" xr3:uid="{1FA9F5F7-D116-43FA-A1DF-133DC6BF0A25}" uniqueName="1" name="Brand " queryTableFieldId="1" dataDxfId="78"/>
     <tableColumn id="2" xr3:uid="{F3803D94-84B7-403E-BA00-D0251BF516BD}" uniqueName="2" name="Model" queryTableFieldId="2" dataDxfId="77"/>
@@ -2174,7 +2192,7 @@
     <tableColumn id="38" xr3:uid="{8C4BB5AE-D1D9-4C25-B65F-17ACFF879C78}" uniqueName="38" name="damaged_left_side" queryTableFieldId="38"/>
     <tableColumn id="39" xr3:uid="{4F7DE766-0CFE-432C-B0AD-7534510A89A5}" uniqueName="39" name="damaged_right_side" queryTableFieldId="39"/>
     <tableColumn id="40" xr3:uid="{702CDD56-BC89-4431-A042-0FB64AFD5F89}" uniqueName="40" name="damaged_interior" queryTableFieldId="40"/>
-    <tableColumn id="41" xr3:uid="{2C2DD1C4-1F06-4625-A0FA-07A3260D5D7E}" uniqueName="41" name="damaged_exterior" queryTableFieldId="41" dataDxfId="0"/>
+    <tableColumn id="41" xr3:uid="{2C2DD1C4-1F06-4625-A0FA-07A3260D5D7E}" uniqueName="41" name="damaged_exterior" queryTableFieldId="41" dataDxfId="70"/>
     <tableColumn id="43" xr3:uid="{B1A4836A-43CF-443F-A8DB-2405AA04F5FB}" uniqueName="43" name="damaged_tire" queryTableFieldId="43"/>
     <tableColumn id="44" xr3:uid="{CC159901-28E3-4884-AF31-E398C4633534}" uniqueName="44" name="damaged_rim" queryTableFieldId="44"/>
     <tableColumn id="45" xr3:uid="{675A77F0-FB9C-4598-A3C8-938130596085}" uniqueName="45" name="damaged_roof_beam" queryTableFieldId="45"/>
@@ -2190,77 +2208,77 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{464C0279-71F1-4BF4-9DF4-7CF0196916DD}" name="Tabelle1" displayName="Tabelle1" ref="A1:BP21" totalsRowShown="0" headerRowDxfId="70" tableBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{464C0279-71F1-4BF4-9DF4-7CF0196916DD}" name="Tabelle1" displayName="Tabelle1" ref="A1:BP21" totalsRowShown="0" headerRowDxfId="69" tableBorderDxfId="68">
   <autoFilter ref="A1:BP21" xr:uid="{464C0279-71F1-4BF4-9DF4-7CF0196916DD}"/>
   <tableColumns count="68">
-    <tableColumn id="1" xr3:uid="{A1A1988D-7907-4991-8254-73E9A95B71C0}" name="Brand " dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{FD48C8B3-B820-4657-9582-8B8EFC2C6E93}" name="Model" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{314A4582-5B99-4EF8-8BFA-FB6B07AE6EB0}" name="year of manufacture" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{2875336F-C431-443C-9302-6FBD0DBA700F}" name="Engine power (kilowatt)" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{036DA9E1-6070-4346-937B-D07359A9CE7F}" name="Engine power (Horsepower)" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{065E5B36-2392-451B-A7F3-BDC8890AA535}" name="Transmission type" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{D3AF73AC-CA12-483B-AE30-2C495AAB2D28}" name="Emission group" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{02F827BC-C548-4370-A45A-530DFEB82A61}" name="Cubic capacity" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{FB4FF4A3-057A-4E44-ACBB-140EE07917AA}" name=" Number of gears" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{75512263-6F2D-455B-92A1-8E3254417930}" name="CO2 (g/km)" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{F052B071-194F-4AA8-8E22-2386B69275DA}" name="Tank capacity" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{CA0CA011-97B7-482F-985D-838BE884A58B}" name="Date of general inspection" dataDxfId="57"/>
-    <tableColumn id="13" xr3:uid="{84E77574-4747-4FF7-9CBA-CD8DCC523187}" name="Mileage" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{45541807-CCD0-4967-B431-37401826432F}" name="Empty weight (kg)" dataDxfId="55"/>
-    <tableColumn id="15" xr3:uid="{45FEC49E-4BE3-44CB-A9C2-7DDF79F4AE60}" name="Permitted gross weight" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{44D32311-404E-4F1F-899D-6473082835BA}" name="Acceleration (0-100Km/h)" dataDxfId="53"/>
-    <tableColumn id="17" xr3:uid="{F9F26806-10D5-49A2-AB6E-4510594B835C}" name="max_speed_kmh" dataDxfId="52"/>
-    <tableColumn id="18" xr3:uid="{EA9D52AC-8EB2-447B-B755-A1898A458AE6}" name="Region" dataDxfId="51"/>
-    <tableColumn id="19" xr3:uid="{03508BB5-D05B-45FA-9A6E-8373FC59EBF9}" name="Engine type" dataDxfId="50"/>
-    <tableColumn id="20" xr3:uid="{D01E3774-C164-42B3-A99A-60F29CD4C254}" name="next general inspection" dataDxfId="49"/>
-    <tableColumn id="21" xr3:uid="{A4F583AD-A549-4A43-89B5-F67B02D4390F}" name="Color" dataDxfId="48"/>
-    <tableColumn id="22" xr3:uid="{A4C64090-27E2-4A32-BA8F-9DB93818D7B4}" name="Vehicle model" dataDxfId="47"/>
-    <tableColumn id="23" xr3:uid="{E950F44A-21B0-422A-964A-C2D25FB5ABA4}" name="Nber of gears" dataDxfId="46"/>
-    <tableColumn id="24" xr3:uid="{374849C6-0C0B-4AC6-A81D-06742FE450FD}" name="Nber of seats" dataDxfId="45"/>
-    <tableColumn id="25" xr3:uid="{831A7488-9D28-4C55-A28E-9EEFE19D9D32}" name="Nber previous owners" dataDxfId="44"/>
-    <tableColumn id="26" xr3:uid="{73B0207D-F8E1-44CA-B667-8D2F1D00443A}" name="Number of doors" dataDxfId="43"/>
-    <tableColumn id="27" xr3:uid="{61558CF1-5C32-499F-BEC8-61786C85E3E0}" name="First_registration _car" dataDxfId="42"/>
-    <tableColumn id="28" xr3:uid="{CE3334A2-B21A-4109-958B-0BCDB8034CF7}" name="Ready to drive" dataDxfId="41"/>
-    <tableColumn id="29" xr3:uid="{89FC32BE-DACE-4638-A9E6-DA83C1A6D80C}" name="Body style" dataDxfId="40"/>
-    <tableColumn id="30" xr3:uid="{3F946E64-BD79-47C5-BE0F-917B617BF9E0}" name="Tire type" dataDxfId="39"/>
-    <tableColumn id="31" xr3:uid="{058614CB-778E-405A-B102-2F43B3771BB0}" name="Rim type" dataDxfId="38"/>
-    <tableColumn id="32" xr3:uid="{818D86A1-4B5E-4894-9FC7-42E25FC0D632}" name="Rights of third parties" dataDxfId="37"/>
-    <tableColumn id="33" xr3:uid="{FC3C8BBE-C684-4F17-AF1E-83D482D58EFC}" name="Transmission type2" dataDxfId="36"/>
-    <tableColumn id="34" xr3:uid="{7BE192DA-69BD-404E-8B87-9203CCB3668B}" name="Accident history" dataDxfId="35"/>
-    <tableColumn id="35" xr3:uid="{95D9CD39-4DC4-4B72-8156-B74BC7D51633}" name="Sale price" dataDxfId="34"/>
-    <tableColumn id="36" xr3:uid="{25D03765-B96B-46AD-A2A6-396E4063036D}" name="damaged_front" dataDxfId="33"/>
-    <tableColumn id="37" xr3:uid="{2BA86C6B-F31B-48F4-8FAA-F97C34F978D9}" name="damaged_rear" dataDxfId="32"/>
-    <tableColumn id="38" xr3:uid="{6050C93D-2833-4509-B4CE-C68532648B00}" name="damaged_link_side" dataDxfId="31"/>
-    <tableColumn id="39" xr3:uid="{7F85FEC1-EAA1-4008-9F17-9F11E2786F56}" name="damaged_right_side" dataDxfId="30"/>
-    <tableColumn id="40" xr3:uid="{FA17B016-0CC7-40C2-A019-4F001E5669E4}" name="damaged_interior" dataDxfId="29"/>
-    <tableColumn id="41" xr3:uid="{3945DF46-DCD9-4160-9D2C-B92ED5632866}" name="damaged_exterior" dataDxfId="28"/>
-    <tableColumn id="42" xr3:uid="{18BED0C9-53E8-4B04-9ED1-C4AAB598EE72}" name="accessory_missing" dataDxfId="27"/>
-    <tableColumn id="43" xr3:uid="{F80D1AFA-94A4-458A-8E8B-9DCC4A3563D8}" name="damaged_tire" dataDxfId="26"/>
-    <tableColumn id="44" xr3:uid="{3C9D184F-BFBA-433A-8129-2505E383F100}" name="damaged_rim" dataDxfId="25"/>
-    <tableColumn id="45" xr3:uid="{27177A5B-12E2-4470-A2BA-93037F53D663}" name="damaged_roof_beam" dataDxfId="24"/>
-    <tableColumn id="46" xr3:uid="{99E41BA2-14F1-4B70-9675-347C8AF13993}" name="damaged_mirror" dataDxfId="23"/>
-    <tableColumn id="47" xr3:uid="{299C9324-CD25-4635-848D-8785B8020D47}" name="damaged_link_door" dataDxfId="22"/>
-    <tableColumn id="48" xr3:uid="{8A6E45AF-0C4E-47AE-9BD8-8C959609592D}" name="damaged_right_door" dataDxfId="21"/>
-    <tableColumn id="49" xr3:uid="{61C10F49-DF6E-4CE0-A6FB-8B336A7371C7}" name="Nber_of_key" dataDxfId="20"/>
-    <tableColumn id="50" xr3:uid="{7FF1DC36-EA34-4D3C-A31C-E1AEB45AD689}" name="missing_winter_tires" dataDxfId="19"/>
-    <tableColumn id="51" xr3:uid="{75D67058-D20A-4D55-8545-A48A047B6C43}" name="major_inspection_due" dataDxfId="18"/>
-    <tableColumn id="52" xr3:uid="{516E6F6B-4FBB-4DE6-A395-241BE5CB04A0}" name="comfort_features" dataDxfId="17"/>
-    <tableColumn id="53" xr3:uid="{1EFBF167-BBFE-496D-B8C0-BCA06118169F}" name="navigation_sytem" dataDxfId="16"/>
-    <tableColumn id="54" xr3:uid="{5360214A-B0D5-443A-A80E-34D4431C7E7F}" name="safety_features" dataDxfId="15"/>
-    <tableColumn id="55" xr3:uid="{EECB7201-8BEC-42C0-BC41-6E5908A0F922}" name="leasing_car" dataDxfId="14"/>
-    <tableColumn id="56" xr3:uid="{7693219A-373E-4755-8754-2A09A64AEB35}" name="damaged_repair" dataDxfId="13"/>
-    <tableColumn id="57" xr3:uid="{67711BEB-D750-4839-8495-1230DA94FB41}" name="has_winter_package" dataDxfId="12"/>
-    <tableColumn id="58" xr3:uid="{6D4AB53B-50C8-429D-A3AB-5C59D69ADEC6}" name="has_seat_heating_front" dataDxfId="11"/>
-    <tableColumn id="59" xr3:uid="{D6229E9F-EFB0-4A03-B479-F5543F2713E1}" name="has_metallic_paint" dataDxfId="10"/>
-    <tableColumn id="60" xr3:uid="{A7366160-59FD-4A78-9D04-6AB2E0E21C0F}" name="space_saver_spare_wheel" dataDxfId="9"/>
-    <tableColumn id="61" xr3:uid="{1CB89733-7863-4F6B-A9E9-E706C73E3B5A}" name="has_headlight_washer" dataDxfId="8"/>
-    <tableColumn id="62" xr3:uid="{7B04860B-F4BC-42A8-8537-4EC329AB8402}" name="has_foldable_front_passenger_seat" dataDxfId="7"/>
-    <tableColumn id="63" xr3:uid="{B6B60C4C-B279-4F26-9800-3EA8EDAC2F38}" name="has_warning_light" dataDxfId="6"/>
-    <tableColumn id="64" xr3:uid="{00B146C8-8A63-4654-89E2-3A2BCF06B781}" name="license_plate_holder" dataDxfId="5"/>
-    <tableColumn id="65" xr3:uid="{B943754A-2085-4247-B92F-38C36F02DE35}" name="luggage_compartment_safety_net" dataDxfId="4"/>
-    <tableColumn id="66" xr3:uid="{29FD0DEB-13BD-49E9-A109-0E2B0E7F7567}" name="has_height_adjustable_passenger_seat" dataDxfId="3"/>
-    <tableColumn id="67" xr3:uid="{B35A6DE5-47F8-4E00-ABE0-715229A0D6BE}" name="has_foldable_seat_tables" dataDxfId="2"/>
-    <tableColumn id="68" xr3:uid="{88E44D20-0E14-4833-AC97-70BA2EE2365D}" name="has_advertising_foil" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A1A1988D-7907-4991-8254-73E9A95B71C0}" name="Brand " dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{FD48C8B3-B820-4657-9582-8B8EFC2C6E93}" name="Model" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{314A4582-5B99-4EF8-8BFA-FB6B07AE6EB0}" name="year of manufacture" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{2875336F-C431-443C-9302-6FBD0DBA700F}" name="Engine power (kilowatt)" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{036DA9E1-6070-4346-937B-D07359A9CE7F}" name="Engine power (Horsepower)" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{065E5B36-2392-451B-A7F3-BDC8890AA535}" name="Transmission type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{D3AF73AC-CA12-483B-AE30-2C495AAB2D28}" name="Emission group" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{02F827BC-C548-4370-A45A-530DFEB82A61}" name="Cubic capacity" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{FB4FF4A3-057A-4E44-ACBB-140EE07917AA}" name=" Number of gears" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{75512263-6F2D-455B-92A1-8E3254417930}" name="CO2 (g/km)" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{F052B071-194F-4AA8-8E22-2386B69275DA}" name="Tank capacity" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{CA0CA011-97B7-482F-985D-838BE884A58B}" name="Date of general inspection" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{84E77574-4747-4FF7-9CBA-CD8DCC523187}" name="Mileage" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{45541807-CCD0-4967-B431-37401826432F}" name="Empty weight (kg)" dataDxfId="54"/>
+    <tableColumn id="15" xr3:uid="{45FEC49E-4BE3-44CB-A9C2-7DDF79F4AE60}" name="Permitted gross weight" dataDxfId="53"/>
+    <tableColumn id="16" xr3:uid="{44D32311-404E-4F1F-899D-6473082835BA}" name="Acceleration (0-100Km/h)" dataDxfId="52"/>
+    <tableColumn id="17" xr3:uid="{F9F26806-10D5-49A2-AB6E-4510594B835C}" name="max_speed_kmh" dataDxfId="51"/>
+    <tableColumn id="18" xr3:uid="{EA9D52AC-8EB2-447B-B755-A1898A458AE6}" name="Region" dataDxfId="50"/>
+    <tableColumn id="19" xr3:uid="{03508BB5-D05B-45FA-9A6E-8373FC59EBF9}" name="Engine type" dataDxfId="49"/>
+    <tableColumn id="20" xr3:uid="{D01E3774-C164-42B3-A99A-60F29CD4C254}" name="next general inspection" dataDxfId="48"/>
+    <tableColumn id="21" xr3:uid="{A4F583AD-A549-4A43-89B5-F67B02D4390F}" name="Color" dataDxfId="47"/>
+    <tableColumn id="22" xr3:uid="{A4C64090-27E2-4A32-BA8F-9DB93818D7B4}" name="Vehicle model" dataDxfId="46"/>
+    <tableColumn id="23" xr3:uid="{E950F44A-21B0-422A-964A-C2D25FB5ABA4}" name="Nber of gears" dataDxfId="45"/>
+    <tableColumn id="24" xr3:uid="{374849C6-0C0B-4AC6-A81D-06742FE450FD}" name="Nber of seats" dataDxfId="44"/>
+    <tableColumn id="25" xr3:uid="{831A7488-9D28-4C55-A28E-9EEFE19D9D32}" name="Nber previous owners" dataDxfId="43"/>
+    <tableColumn id="26" xr3:uid="{73B0207D-F8E1-44CA-B667-8D2F1D00443A}" name="Number of doors" dataDxfId="42"/>
+    <tableColumn id="27" xr3:uid="{61558CF1-5C32-499F-BEC8-61786C85E3E0}" name="First_registration _car" dataDxfId="41"/>
+    <tableColumn id="28" xr3:uid="{CE3334A2-B21A-4109-958B-0BCDB8034CF7}" name="Ready to drive" dataDxfId="40"/>
+    <tableColumn id="29" xr3:uid="{89FC32BE-DACE-4638-A9E6-DA83C1A6D80C}" name="Body style" dataDxfId="39"/>
+    <tableColumn id="30" xr3:uid="{3F946E64-BD79-47C5-BE0F-917B617BF9E0}" name="Tire type" dataDxfId="38"/>
+    <tableColumn id="31" xr3:uid="{058614CB-778E-405A-B102-2F43B3771BB0}" name="Rim type" dataDxfId="37"/>
+    <tableColumn id="32" xr3:uid="{818D86A1-4B5E-4894-9FC7-42E25FC0D632}" name="Rights of third parties" dataDxfId="36"/>
+    <tableColumn id="33" xr3:uid="{FC3C8BBE-C684-4F17-AF1E-83D482D58EFC}" name="Transmission type2" dataDxfId="35"/>
+    <tableColumn id="34" xr3:uid="{7BE192DA-69BD-404E-8B87-9203CCB3668B}" name="Accident history" dataDxfId="34"/>
+    <tableColumn id="35" xr3:uid="{95D9CD39-4DC4-4B72-8156-B74BC7D51633}" name="Sale price" dataDxfId="33"/>
+    <tableColumn id="36" xr3:uid="{25D03765-B96B-46AD-A2A6-396E4063036D}" name="damaged_front" dataDxfId="32"/>
+    <tableColumn id="37" xr3:uid="{2BA86C6B-F31B-48F4-8FAA-F97C34F978D9}" name="damaged_rear" dataDxfId="31"/>
+    <tableColumn id="38" xr3:uid="{6050C93D-2833-4509-B4CE-C68532648B00}" name="damaged_link_side" dataDxfId="30"/>
+    <tableColumn id="39" xr3:uid="{7F85FEC1-EAA1-4008-9F17-9F11E2786F56}" name="damaged_right_side" dataDxfId="29"/>
+    <tableColumn id="40" xr3:uid="{FA17B016-0CC7-40C2-A019-4F001E5669E4}" name="damaged_interior" dataDxfId="28"/>
+    <tableColumn id="41" xr3:uid="{3945DF46-DCD9-4160-9D2C-B92ED5632866}" name="damaged_exterior" dataDxfId="27"/>
+    <tableColumn id="42" xr3:uid="{18BED0C9-53E8-4B04-9ED1-C4AAB598EE72}" name="accessory_missing" dataDxfId="26"/>
+    <tableColumn id="43" xr3:uid="{F80D1AFA-94A4-458A-8E8B-9DCC4A3563D8}" name="damaged_tire" dataDxfId="25"/>
+    <tableColumn id="44" xr3:uid="{3C9D184F-BFBA-433A-8129-2505E383F100}" name="damaged_rim" dataDxfId="24"/>
+    <tableColumn id="45" xr3:uid="{27177A5B-12E2-4470-A2BA-93037F53D663}" name="damaged_roof_beam" dataDxfId="23"/>
+    <tableColumn id="46" xr3:uid="{99E41BA2-14F1-4B70-9675-347C8AF13993}" name="damaged_mirror" dataDxfId="22"/>
+    <tableColumn id="47" xr3:uid="{299C9324-CD25-4635-848D-8785B8020D47}" name="damaged_link_door" dataDxfId="21"/>
+    <tableColumn id="48" xr3:uid="{8A6E45AF-0C4E-47AE-9BD8-8C959609592D}" name="damaged_right_door" dataDxfId="20"/>
+    <tableColumn id="49" xr3:uid="{61C10F49-DF6E-4CE0-A6FB-8B336A7371C7}" name="Nber_of_key" dataDxfId="19"/>
+    <tableColumn id="50" xr3:uid="{7FF1DC36-EA34-4D3C-A31C-E1AEB45AD689}" name="missing_winter_tires" dataDxfId="18"/>
+    <tableColumn id="51" xr3:uid="{75D67058-D20A-4D55-8545-A48A047B6C43}" name="major_inspection_due" dataDxfId="17"/>
+    <tableColumn id="52" xr3:uid="{516E6F6B-4FBB-4DE6-A395-241BE5CB04A0}" name="comfort_features" dataDxfId="16"/>
+    <tableColumn id="53" xr3:uid="{1EFBF167-BBFE-496D-B8C0-BCA06118169F}" name="navigation_sytem" dataDxfId="15"/>
+    <tableColumn id="54" xr3:uid="{5360214A-B0D5-443A-A80E-34D4431C7E7F}" name="safety_features" dataDxfId="14"/>
+    <tableColumn id="55" xr3:uid="{EECB7201-8BEC-42C0-BC41-6E5908A0F922}" name="leasing_car" dataDxfId="13"/>
+    <tableColumn id="56" xr3:uid="{7693219A-373E-4755-8754-2A09A64AEB35}" name="damaged_repair" dataDxfId="12"/>
+    <tableColumn id="57" xr3:uid="{67711BEB-D750-4839-8495-1230DA94FB41}" name="has_winter_package" dataDxfId="11"/>
+    <tableColumn id="58" xr3:uid="{6D4AB53B-50C8-429D-A3AB-5C59D69ADEC6}" name="has_seat_heating_front" dataDxfId="10"/>
+    <tableColumn id="59" xr3:uid="{D6229E9F-EFB0-4A03-B479-F5543F2713E1}" name="has_metallic_paint" dataDxfId="9"/>
+    <tableColumn id="60" xr3:uid="{A7366160-59FD-4A78-9D04-6AB2E0E21C0F}" name="space_saver_spare_wheel" dataDxfId="8"/>
+    <tableColumn id="61" xr3:uid="{1CB89733-7863-4F6B-A9E9-E706C73E3B5A}" name="has_headlight_washer" dataDxfId="7"/>
+    <tableColumn id="62" xr3:uid="{7B04860B-F4BC-42A8-8537-4EC329AB8402}" name="has_foldable_front_passenger_seat" dataDxfId="6"/>
+    <tableColumn id="63" xr3:uid="{B6B60C4C-B279-4F26-9800-3EA8EDAC2F38}" name="has_warning_light" dataDxfId="5"/>
+    <tableColumn id="64" xr3:uid="{00B146C8-8A63-4654-89E2-3A2BCF06B781}" name="license_plate_holder" dataDxfId="4"/>
+    <tableColumn id="65" xr3:uid="{B943754A-2085-4247-B92F-38C36F02DE35}" name="luggage_compartment_safety_net" dataDxfId="3"/>
+    <tableColumn id="66" xr3:uid="{29FD0DEB-13BD-49E9-A109-0E2B0E7F7567}" name="has_height_adjustable_passenger_seat" dataDxfId="2"/>
+    <tableColumn id="67" xr3:uid="{B35A6DE5-47F8-4E00-ABE0-715229A0D6BE}" name="has_foldable_seat_tables" dataDxfId="1"/>
+    <tableColumn id="68" xr3:uid="{88E44D20-0E14-4833-AC97-70BA2EE2365D}" name="has_advertising_foil" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2583,7 +2601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F89A35D-27C2-4F50-86F5-3909E2573C92}">
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.36328125" bestFit="1" customWidth="1"/>
@@ -2711,7 +2729,7 @@
       <c r="S1" t="s">
         <v>60</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="T1" s="16" t="s">
         <v>77</v>
       </c>
       <c r="U1" t="s">
@@ -2800,7 +2818,7 @@
       <c r="S2">
         <v>1</v>
       </c>
-      <c r="T2" s="17">
+      <c r="T2" s="16">
         <v>1</v>
       </c>
       <c r="U2">
@@ -2889,7 +2907,7 @@
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="16">
         <v>0</v>
       </c>
       <c r="U3">
@@ -2978,7 +2996,7 @@
       <c r="S4">
         <v>1</v>
       </c>
-      <c r="T4" s="17">
+      <c r="T4" s="16">
         <v>1</v>
       </c>
       <c r="U4">
@@ -3067,7 +3085,7 @@
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5" s="17">
+      <c r="T5" s="16">
         <v>0</v>
       </c>
       <c r="U5">
@@ -3156,7 +3174,7 @@
       <c r="S6">
         <v>1</v>
       </c>
-      <c r="T6" s="17">
+      <c r="T6" s="16">
         <v>1</v>
       </c>
       <c r="U6">
@@ -3245,7 +3263,7 @@
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7" s="17">
+      <c r="T7" s="16">
         <v>0</v>
       </c>
       <c r="U7">
@@ -3334,7 +3352,7 @@
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8" s="17">
+      <c r="T8" s="16">
         <v>0</v>
       </c>
       <c r="U8">
@@ -3423,7 +3441,7 @@
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9" s="17">
+      <c r="T9" s="16">
         <v>0</v>
       </c>
       <c r="U9">
@@ -3512,7 +3530,7 @@
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10" s="17">
+      <c r="T10" s="16">
         <v>0</v>
       </c>
       <c r="U10">
@@ -3601,7 +3619,7 @@
       <c r="S11">
         <v>1</v>
       </c>
-      <c r="T11" s="17">
+      <c r="T11" s="16">
         <v>1</v>
       </c>
       <c r="U11">
@@ -3690,7 +3708,7 @@
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12" s="17">
+      <c r="T12" s="16">
         <v>0</v>
       </c>
       <c r="U12">
@@ -3779,7 +3797,7 @@
       <c r="S13">
         <v>1</v>
       </c>
-      <c r="T13" s="17">
+      <c r="T13" s="16">
         <v>1</v>
       </c>
       <c r="U13">
@@ -3868,7 +3886,7 @@
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14" s="17">
+      <c r="T14" s="16">
         <v>0</v>
       </c>
       <c r="U14">
@@ -3957,7 +3975,7 @@
       <c r="S15">
         <v>1</v>
       </c>
-      <c r="T15" s="17">
+      <c r="T15" s="16">
         <v>1</v>
       </c>
       <c r="U15">
@@ -4046,7 +4064,7 @@
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16" s="17">
+      <c r="T16" s="16">
         <v>0</v>
       </c>
       <c r="U16">
@@ -4135,7 +4153,7 @@
       <c r="S17">
         <v>1</v>
       </c>
-      <c r="T17" s="17">
+      <c r="T17" s="16">
         <v>1</v>
       </c>
       <c r="U17">
@@ -4224,7 +4242,7 @@
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18" s="17">
+      <c r="T18" s="16">
         <v>1</v>
       </c>
       <c r="U18">
@@ -4313,7 +4331,7 @@
       <c r="S19">
         <v>1</v>
       </c>
-      <c r="T19" s="17">
+      <c r="T19" s="16">
         <v>1</v>
       </c>
       <c r="U19">
@@ -4402,7 +4420,7 @@
       <c r="S20">
         <v>1</v>
       </c>
-      <c r="T20" s="17">
+      <c r="T20" s="16">
         <v>0</v>
       </c>
       <c r="U20">
@@ -4491,7 +4509,7 @@
       <c r="S21">
         <v>1</v>
       </c>
-      <c r="T21" s="17">
+      <c r="T21" s="16">
         <v>1</v>
       </c>
       <c r="U21">
@@ -4580,7 +4598,7 @@
       <c r="S22">
         <v>1</v>
       </c>
-      <c r="T22" s="17">
+      <c r="T22" s="16">
         <v>1</v>
       </c>
       <c r="U22">
@@ -4669,7 +4687,7 @@
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23" s="17">
+      <c r="T23" s="16">
         <v>1</v>
       </c>
       <c r="U23">
@@ -4758,7 +4776,7 @@
       <c r="S24">
         <v>0</v>
       </c>
-      <c r="T24" s="17">
+      <c r="T24" s="16">
         <v>1</v>
       </c>
       <c r="U24">
@@ -4847,7 +4865,7 @@
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25" s="17">
+      <c r="T25" s="16">
         <v>0</v>
       </c>
       <c r="U25">
@@ -4936,7 +4954,7 @@
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26" s="17">
+      <c r="T26" s="16">
         <v>0</v>
       </c>
       <c r="U26">
@@ -5025,7 +5043,7 @@
       <c r="S27">
         <v>0</v>
       </c>
-      <c r="T27" s="17">
+      <c r="T27" s="16">
         <v>0</v>
       </c>
       <c r="U27">
@@ -5114,7 +5132,7 @@
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28" s="17">
+      <c r="T28" s="16">
         <v>1</v>
       </c>
       <c r="U28">
@@ -5203,7 +5221,7 @@
       <c r="S29">
         <v>0</v>
       </c>
-      <c r="T29" s="17">
+      <c r="T29" s="16">
         <v>0</v>
       </c>
       <c r="U29">
@@ -5292,7 +5310,7 @@
       <c r="S30">
         <v>1</v>
       </c>
-      <c r="T30" s="17">
+      <c r="T30" s="16">
         <v>1</v>
       </c>
       <c r="U30">
@@ -5381,7 +5399,7 @@
       <c r="S31">
         <v>0</v>
       </c>
-      <c r="T31" s="17">
+      <c r="T31" s="16">
         <v>0</v>
       </c>
       <c r="U31">
@@ -5470,7 +5488,7 @@
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32" s="17">
+      <c r="T32" s="16">
         <v>0</v>
       </c>
       <c r="U32">
@@ -5559,7 +5577,7 @@
       <c r="S33">
         <v>0</v>
       </c>
-      <c r="T33" s="17">
+      <c r="T33" s="16">
         <v>1</v>
       </c>
       <c r="U33">
@@ -5648,7 +5666,7 @@
       <c r="S34">
         <v>0</v>
       </c>
-      <c r="T34" s="17">
+      <c r="T34" s="16">
         <v>1</v>
       </c>
       <c r="U34">
@@ -5737,7 +5755,7 @@
       <c r="S35">
         <v>1</v>
       </c>
-      <c r="T35" s="17">
+      <c r="T35" s="16">
         <v>0</v>
       </c>
       <c r="U35">
@@ -5826,7 +5844,7 @@
       <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36" s="17">
+      <c r="T36" s="16">
         <v>1</v>
       </c>
       <c r="U36">
@@ -5915,7 +5933,7 @@
       <c r="S37">
         <v>1</v>
       </c>
-      <c r="T37" s="17">
+      <c r="T37" s="16">
         <v>1</v>
       </c>
       <c r="U37">
@@ -6004,7 +6022,7 @@
       <c r="S38">
         <v>0</v>
       </c>
-      <c r="T38" s="17">
+      <c r="T38" s="16">
         <v>1</v>
       </c>
       <c r="U38">
@@ -6036,10 +6054,10 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
+      <c r="A39" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" t="s">
         <v>199</v>
       </c>
       <c r="C39">
@@ -6051,13 +6069,13 @@
       <c r="E39">
         <v>120</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="F39" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="14">
         <v>89500</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" t="s">
         <v>200</v>
       </c>
       <c r="I39" s="12">
@@ -6066,13 +6084,13 @@
       <c r="J39">
         <v>2</v>
       </c>
-      <c r="K39" s="16" t="s">
+      <c r="K39" t="s">
         <v>201</v>
       </c>
-      <c r="L39" s="16" t="s">
+      <c r="L39" t="s">
         <v>44</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="M39" t="s">
         <v>34</v>
       </c>
       <c r="N39">
@@ -6081,7 +6099,7 @@
       <c r="O39">
         <v>0</v>
       </c>
-      <c r="P39" s="17">
+      <c r="P39" s="16">
         <v>1</v>
       </c>
       <c r="Q39">
@@ -6093,7 +6111,7 @@
       <c r="S39">
         <v>0</v>
       </c>
-      <c r="T39" s="17">
+      <c r="T39" s="16">
         <v>0</v>
       </c>
       <c r="U39">
@@ -6125,10 +6143,10 @@
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
+      <c r="A40" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" t="s">
         <v>131</v>
       </c>
       <c r="C40">
@@ -6140,13 +6158,13 @@
       <c r="E40">
         <v>140</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" t="s">
         <v>19</v>
       </c>
       <c r="G40">
         <v>62000</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" t="s">
         <v>200</v>
       </c>
       <c r="I40" s="12">
@@ -6155,13 +6173,13 @@
       <c r="J40">
         <v>3</v>
       </c>
-      <c r="K40" s="16" t="s">
+      <c r="K40" t="s">
         <v>43</v>
       </c>
-      <c r="L40" s="16" t="s">
+      <c r="L40" t="s">
         <v>139</v>
       </c>
-      <c r="M40" s="16" t="s">
+      <c r="M40" t="s">
         <v>34</v>
       </c>
       <c r="N40" s="14">
@@ -6170,7 +6188,7 @@
       <c r="O40">
         <v>0</v>
       </c>
-      <c r="P40" s="17">
+      <c r="P40" s="16">
         <v>1</v>
       </c>
       <c r="Q40">
@@ -6182,7 +6200,7 @@
       <c r="S40">
         <v>1</v>
       </c>
-      <c r="T40" s="17">
+      <c r="T40" s="16">
         <v>1</v>
       </c>
       <c r="U40">
@@ -6211,6 +6229,273 @@
       </c>
       <c r="AC40" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A41" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C41">
+        <v>2018</v>
+      </c>
+      <c r="D41">
+        <v>51</v>
+      </c>
+      <c r="E41">
+        <v>69</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G41">
+        <v>55756</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="I41" s="12">
+        <v>46631</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="L41" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M41" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N41">
+        <v>12499</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41" s="16">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>1</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>1</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42">
+        <v>2025</v>
+      </c>
+      <c r="D42">
+        <v>96</v>
+      </c>
+      <c r="E42">
+        <v>131</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="I42" s="12">
+        <v>46722</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L42" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="M42" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N42">
+        <v>25845</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42" s="16">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>1</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43">
+        <v>2015</v>
+      </c>
+      <c r="D43">
+        <v>70</v>
+      </c>
+      <c r="E43">
+        <v>95</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43">
+        <v>150000</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="12">
+        <v>46055</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N43">
+        <v>4990</v>
+      </c>
+      <c r="O43">
+        <v>1</v>
+      </c>
+      <c r="P43" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <v>1</v>
+      </c>
+      <c r="T43" s="16">
+        <v>1</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
